--- a/Scraped Tweets - Nigeria/Deyemi Okanlawon_scope_relevant.xlsx
+++ b/Scraped Tweets - Nigeria/Deyemi Okanlawon_scope_relevant.xlsx
@@ -14,72 +14,423 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="139">
   <si>
     <t>text</t>
   </si>
   <si>
-    <t>If you're not yet financially buoyant perhaps it is wise take a break from "serious" relationship and focus on building yourself... this message from the federal association of common sense is for men &amp;amp; women #openletter #butwhatdoiknow</t>
+    <t>As a father (and son) I'm very aware of the extremes parents will go to save their child and with the current harsh economy, CBN policies that led to last year's cash crunch and the prevalent failures in banking operation all highlighted in our movie #3WorkingDays...</t>
+  </si>
+  <si>
+    <t>If you're not yet financially buoyant perhaps it is wise take a break from "serious" relationship and focus on building yourself... this message from the federal association of common sense is for men &amp; women #openletter #butwhatdoiknow</t>
+  </si>
+  <si>
+    <t>As with women, it's perfectly fine for and the right of men to also speak out and to speak their "truth". Also it's even ok for the "truth" to evolve/change over time... it is solely the responsibility of those in relationship with them to decide if it's a "truth" they accept</t>
   </si>
   <si>
     <t>There are generally two types of guys... a man or a man-child. One is of high value, the other is toxic</t>
   </si>
   <si>
-    <t>It's like a lot of women &amp;amp; men nowadays are just stark raving mad! This one justifying cheating cos of her money needs &amp;amp; then breaking up, the other justifying cheating cos he can cheat &amp;amp; remain in a relationship! Nobody dey holy but even if you do it what's wrong is wrong na! 🤦🏽‍♂️</t>
+    <t>I'm more concerned about being able to take care of my wife and 3 boys. God bless you and yours and me and mine! 🙏🏾 #3WorkingDays #nowincinemas</t>
+  </si>
+  <si>
+    <t>Faith is not (talking about) the thing you desire, it's the masterplan/steps you have developed to get it. Setting a goal is one thing, creating a system to increase the chance of success is another. Don't just tell me what you want to achieve, tell me how you plan to get it 🙏🏾</t>
+  </si>
+  <si>
+    <t>It's like a lot of women &amp; men nowadays are just stark raving mad! This one justifying cheating cos of her money needs &amp; then breaking up, the other justifying cheating cos he can cheat &amp; remain in a relationship! Nobody dey holy but even if you do it what's wrong is wrong na! 🤦🏽‍♂️</t>
   </si>
   <si>
     <t>Oh, marriage is easy... na spouse(s) wey no get sense dey make am hard! 🚶🏽‍♂️</t>
   </si>
   <si>
+    <t>Yet we all know exactly how this wld have played out if it was a man who *publishes private texts* between him and his gf, calling her out for asking him to respect her boundaries with his opp gender *friends and colleagues*</t>
+  </si>
+  <si>
+    <t>7 Male Personalities Alpha - fearless trailblazers Beta - kind, gentle souls Sigma - transgressive leaders Delta - responsible companions Zeta - nonconformist creatives Gamma - charismatic nomads Omega - sharp intellectuals</t>
+  </si>
+  <si>
+    <t>Let's try and remember that mental health decline from focusing only on all that's wrong causes ppl to lose hope in the future and can lead to so many silly choices... if we do mental health checkup for this country walahi nobody go pass even me! 🥺</t>
+  </si>
+  <si>
+    <t>Prayer for Nigerian men... may we have much more money than our wives, mothers and sisters can spend! Amen 🙏</t>
+  </si>
+  <si>
+    <t>Bros if na real life "many men shall fall again"... 😡</t>
+  </si>
+  <si>
     <t>Man will pack light ("7 shirts for 7 days")... wife will pack heavy ("you never know what you'll need"). Guess who will now suffer at the airport! 👀🚶🏽‍♂️ #justiceformen</t>
   </si>
   <si>
-    <t>Financially buoyant - enough to take care of your, hv some savings/assets, hv some to give to those who raised you, &amp;amp; finally have some to spare to give ease in your relationship. No be this level professional leeches/diggers (m/f) dey find &amp;amp; you sef must learn to code yourself !</t>
-  </si>
-  <si>
-    <t>@LoukmanAli Sigh... I know this childhood trauma all too well!</t>
+    <t>Financially buoyant - enough to take care of your, hv some savings/assets, hv some to give to those who raised you, &amp; finally have some to spare to give ease in your relationship. No be this level professional leeches/diggers (m/f) dey find &amp; you sef must learn to code yourself !</t>
+  </si>
+  <si>
+    <t>My mother always told me to respect my elders! 🤦🏽‍♂️</t>
+  </si>
+  <si>
+    <t>Or to put it in Gen Z parlance... Faith without "workings" is dead! 😂</t>
+  </si>
+  <si>
+    <t>Sadly it's ppl who were likely victims of poor parenting. Abeg leave me make I deal with them ♥️🙏🏾</t>
+  </si>
+  <si>
+    <t>Perhaps self control (for some of us guys) could be 90% putting a process around oneself that helps avoid unwanted situations?</t>
+  </si>
+  <si>
+    <t>My best quote ever... "I KNOW OF NO MORE ENCOURAGING FACT THAN THE UNQUESTIONABLE ABILITY OF MAN TO ELEVATE HIMSELF BY CONSCIOUS ENDEAVOR" ~ HENRY DAVID THOREAU</t>
+  </si>
+  <si>
+    <t>Quit acting in Aug 2019, joined as head of marketing. I was disillusioned about being an actor in Nollywood. In 2020 work halted cos of the pandem*c so I took some film projects to take care of my fam. You know the rest... #Faith #evenwhenyougiveupGodneverquits</t>
+  </si>
+  <si>
+    <t>Sigh... I know this childhood trauma all too well!</t>
+  </si>
+  <si>
+    <t>Since we are now all rude pls at what age gap can one realistically say to a Nigerian youth that I'm old enough to be your father... and then proceed to direct your comments at the ppl in their family who are your mate? 😂😂😂</t>
+  </si>
+  <si>
+    <t>My father always told me to cut my coat according to my size... your trouble pass my own! 😂</t>
+  </si>
+  <si>
+    <t>Guy! As in wokeness and intelligence are obviously not the same thing... especially our Nigerian version of wokeness 😂😂</t>
+  </si>
+  <si>
+    <t>Social media shaming and bullying ppl into submission seems to be the order of the day... until one mad person in authority turns off the Internet! 🤦🏽‍♂️</t>
+  </si>
+  <si>
+    <t>Everything that cld go wrong went wrong, all perfectly laid plans failed &amp; still You showed up for me &amp; granted Grace to do the undoable, Wisdom to solve the impossible &amp; favour in the eyes of Helpers! Father Lord I am humbled cos how can I explain this! 🥲🙏🏾 #AllsFairInLove</t>
+  </si>
+  <si>
+    <t>Only when you go in search of my stance on this and relationship with her will you realise how daft this tweet is... but pls keep trying to sound wise 😊 #wereythinksaynahimtype #fakesocialmedialove #wedeydoforhere</t>
+  </si>
+  <si>
+    <t>According to the 2024 consumer research carried out by the A.S.H.E.W.O. Nigeria, it was observed that the av. Nigerian of a particular gender rated offing-shirt as top 3 on their customer satisfaction index! Tenx! #asunanorateme #whenibegoodboy #evenifnamtzionfeem #igooffshirt 😂</t>
   </si>
   <si>
     <t>If a woman/wife asks her man/husband "who is the most beautiful woman in the world?" What do you do?</t>
   </si>
   <si>
+    <t>Friend: Deyemi I'm now in therapy and there's something I need to tell you Me: Wow.. lemme guess - your therapist quit and now you're her therapist? Friend: With friends like you no wonder I'm nuts! 😂 Deyemi: We're all nuts together. Love you man, I dey here for you! 🙏</t>
+  </si>
+  <si>
     <t>My dad once told me that if a mad man starts yelling at or insulting you on the street the moment you join words with him you will also be considered mad - na why I no dey ans some ppl for social media. . . . Pssst! My dad said no such thing but I'm sure you get the gist! 😂</t>
   </si>
   <si>
+    <t>A few drivers have tried to turn down payments cos they are fans. I always refuse except for one time a young guy insisted that it was a seed &amp; asked for any advice I was willing to share... I shared my story &amp; tweet below - he cried, said I had just given him hope</t>
+  </si>
+  <si>
+    <t>Pls when you kwarupt children are counting "rounds" is it the man or the woman you use to count? Tag your kwarupt friends to answer... I start with</t>
+  </si>
+  <si>
+    <t>Normally I no get wahala but wetin my eye see while making #AllsFairInLove from story development to pre-production to production to post-production to distribution &amp; marketing, forced me to take a stance.... what will you have done?</t>
+  </si>
+  <si>
     <t>Just saw a cute relationship post... girl posted video of her new boyfriend - who also happens to be her bestie's recent (ex)boyfriend/baby daddy. Congrats to them all 🙂</t>
   </si>
   <si>
+    <t>My back is still bleeding from the multiple stabs... from ppl I called friends, colleagues, partners o! Me wey no get bad mind towards anyone! It is well... the film don land! #AllsFairInLove</t>
+  </si>
+  <si>
+    <t>after playing for just over an hour, my 7 yr old just beat me in chess and now I won't hear the last of it. See wetin you don cause 👀🚶🏽‍♂️</t>
+  </si>
+  <si>
+    <t>Yes o! Before one sick person starts imagining things, claims it's reality then ppl starts talking abt "so he's the way he is in movies", "let her speak her truth". Lie go don go far b4 truth catch up... on top small career wey just dey start! God abeg o! 🙏🏾</t>
+  </si>
+  <si>
+    <t>My mum &amp; her older brother had a major issue that lingered over 10yrs. He fell ill recently so I urged &amp; arranged for her to visit last week - he passed away yesterday. Now I'm out of town &amp; don't know how to tell her. Don't waste precious time fighting... you know what to do</t>
+  </si>
+  <si>
+    <t>That energy you spent envying and plotting how to make others stumble would have been better spent battling your own fears, eliminating your own obstacles, tacking your own insecurities, healing from your own trauma and powering your own dreams!</t>
+  </si>
+  <si>
+    <t>You really can't be trying to be friends with a Yoruba man and talk smack about Amala 🙄</t>
+  </si>
+  <si>
+    <t>Guy! Sarcasm can get you offed in Naija! 😂😂😂</t>
+  </si>
+  <si>
+    <t>Me: Sha no go do BBL with the money She: As in BBL registration fee? Me: No na, e go reach to do one yanch She: Ah Me: Yes na... you go do the other later! She: Loooool</t>
+  </si>
+  <si>
     <t>Somewhere in here is perhaps one of the secrets to selecting a spouse</t>
   </si>
   <si>
+    <t>If in the eventuality of a divorce you get half of what I worked hard for plus alimony and child support then maybe I have a right to set my boundaries. And perhaps there lies the true source of the bitterness... 😊</t>
+  </si>
+  <si>
+    <t>This world is designed to kill men... take a minute to think this through 🚶🏽‍♂️</t>
+  </si>
+  <si>
+    <t>So happy for Tiwi &amp; KR... to anyone who falls in love with and chooses a spouse in the public space I pray God protects you from the evil in the hearts of many and grants you peace beyond understanding... because Nigerians will test you! 😂</t>
+  </si>
+  <si>
     <t>May we be able to give our children better childhood experiences than the ones we had! #ToWhomItMayConcern 🙏🏽</t>
   </si>
   <si>
+    <t>Everyone should feel free to love and date anyone at any time/stage of their lives if they so choose... but perhaps for more serious (intentional, committed) relationships you may want to approach things slightly different? 💁‍♀️</t>
+  </si>
+  <si>
+    <t>#aswedeydotherightthing #bysupportinggirlsandwomen #abegonceinawhile #makewedeyremember #tosupportusboysandmentoo #eppmewatchmyfeemwithfriendsandfam #Godblessyouasyoudoso</t>
+  </si>
+  <si>
+    <t>I for say loyalty but they say it can't be bought... 😂</t>
+  </si>
+  <si>
+    <t>And I'm almost certain you have ppl at home who tried to raise you right 😊 #theyfailedbutwecantblamethem</t>
+  </si>
+  <si>
+    <t>He was bullied as a spoilt fat rich kid and Uncle B ensured he got paramilitary and martial arts training... but he never healed #backstory</t>
+  </si>
+  <si>
+    <t>Yh... sad! Is he suing? Will the accuser be arrested?</t>
+  </si>
+  <si>
+    <t>We the Outstanding Men of DANG are waiting for your words of encouragement too... 😏😂 #3WorkingDays #stillincinemas</t>
+  </si>
+  <si>
+    <t>I suspect these days a lot more ppl see and seek fame as an indicator of success and desire it. Maybe posting (marketing) them gives a sense of popularity 🙂</t>
+  </si>
+  <si>
     <t>Love is less about what you get... more about what you give!</t>
   </si>
   <si>
+    <t>Na true but if we are all held accountable and get punished for our stupidity on social media we plenty wey go rot for cell! 🥺</t>
+  </si>
+  <si>
+    <t>Funny how people can have all the trappings of success and seem happy.... and so it's so much harder to notice how horribly depressed they are!</t>
+  </si>
+  <si>
+    <t>Let no one lie to you... we all seek validation often from the wrong places, but when it's right... God knows it's sooooo riiiiight!!! I wish everyone of you here excruciatingly overwhelming joy in your life, your relationships and the work of your hands! 🙏🏾</t>
+  </si>
+  <si>
+    <t>Blood (you share with family) is thicker than water (you share with friends)... hence it's so much harder to decipher the motives of family than it is to see through friends - Deyemi Okanlawon</t>
+  </si>
+  <si>
+    <t>A mentor once told me... "two broke ppl cannot help each other". 😎</t>
+  </si>
+  <si>
+    <t>That one na for you newlyweds! Awa ti pe ninu kini yi! 😂😂</t>
+  </si>
+  <si>
+    <t>No matter the your skill or strategy producers ultimately decide whether or not to hire you. So as you work on the craft and the business of acting also take out time to pray, speak positive words and and take actions that wld attract the lavish display of God's favour</t>
+  </si>
+  <si>
+    <t>Let's not allow this "I want to blow" mentality frustrate us, let's do the work. A word is enough for the wise. 🙏🏾</t>
+  </si>
+  <si>
+    <t>Lol... women really and truly love women! Na una go still taya! 😂😂😂 #trulytrulytruly</t>
+  </si>
+  <si>
+    <t>After wks of sch lessons, playing on my phone &amp; telling him moves from the sideline I finally bought a chessboard for my son &amp; we played our 1st game... what was meant to be an easy schooling turned into almost an hour of playing a pretty tasking game! I sha won, thank God! 🤦🏽‍♂️🚶🏽‍♂️</t>
+  </si>
+  <si>
     <t>Find and remain in the path of love and surround yourself with wise, loving ppl only. In a (social media) world filled with so much hate and hateful people.... your job is not to fight or become like them but to fight with all you have not to let it contaminate you! #ichooselove</t>
   </si>
   <si>
+    <t>My sister! I can't thank you enough for the love and support you've shown me through the years. I'm grateful for your advice and words of encouragement that kept me going despite the challenges I encountered while producing #AllsFairInLove. God bless you ♥️🙏🏾</t>
+  </si>
+  <si>
     <t>A few weeks ago I finally paid off one loan wifey gave me so today, when I saw one funny post on IG, I sent her some cash and said "go spoil yourself"... me that I know she won't spend it and it'll end up being a loan to me with in-kind interest! Oshey GMD #WifeyBankPlc 👀🙄🤦🏽‍♂️😂</t>
   </si>
   <si>
+    <t>Be careful who you accept help from. Some offer support just so they can get close enough to harm you! #AllsFairInLove #nowincinemas</t>
+  </si>
+  <si>
+    <t>Self defense perhaps? Sigh... this won't end well sha!</t>
+  </si>
+  <si>
+    <t>Actually she doesn't have more to lose... he does, hence the appeal</t>
+  </si>
+  <si>
+    <t>The problem was with the lie or the obviousness of it? Cos everyone kinda lies right?</t>
+  </si>
+  <si>
+    <t>Whether you do good or you do bad you may fail or succeed... better to just do you! 🙂</t>
+  </si>
+  <si>
+    <t>I was on the regular path, didn't like the direction my life was heading.... so, in the hope of a better outcome, I took the road less traveled. Thankful for growth 🙏🏾 #AllsFairInLove #comingtocinemas #Feb14</t>
+  </si>
+  <si>
+    <t>Dear socialmediazens, today try not to be that person who stabs others in the place of their pain with shards of your brokenness...</t>
+  </si>
+  <si>
     <t>If you have a boyfriend or girlfriend and someone asks if you are single what's the answer?</t>
   </si>
   <si>
-    <t>@Declectic I believe this story because I know say person wey born you go fit get power do this kind thing! Supermom! 😂♥️</t>
+    <t>He was too involved in the physical world, the lust of the flesh, to fully transcend</t>
+  </si>
+  <si>
+    <t>Na this kind life dey make youth wan do yahoo yahoo! 😂</t>
+  </si>
+  <si>
+    <t>I did everything in my power, got into major debt, poor treatment by cast and crew, not been able to sleep for days! What more can a human do? I DID MY PART! All they had to do was FLIPPING DO THEIRS!!! #AllsFairInLove</t>
+  </si>
+  <si>
+    <t>I've always assumed God operates outside of our time-bound realm and His blessings always exist in the NOW.... perhaps it's our knowledge &amp; understanding of this &amp; our ability to manifest these presently-existing blessings that determine our experience of His Grace! 🙏🏾</t>
+  </si>
+  <si>
+    <t>Lool... a lot of negativity thrives on Twitter so I tweeted about my problems on set. #AllsFairInLove</t>
+  </si>
+  <si>
+    <t>I believe this story because I know say person wey born you go fit get power do this kind thing! Supermom! 😂♥️</t>
+  </si>
+  <si>
+    <t>Piling... some saw the vid and looked on, others chose to expose what's inside them! 😊</t>
+  </si>
+  <si>
+    <t>Remember this... just cos you're not competing with them doesn't mean they are not competing with you. Be wiser!</t>
+  </si>
+  <si>
+    <t>My dear sister , I know you to be very kind, loving person &amp; also know that beyond filing a petition you have neither the intention nor the power to force an arrest so I ask that you pls temper justice with mercy.</t>
+  </si>
+  <si>
+    <t>Me I'm just waiting for the further outrage if he slams her with a well deserved lawsuit for maliciously trying to tarnish his public image and livelihood like was done to Johnny Depp</t>
   </si>
   <si>
     <t>It clearly started with grooming... waiting to see how it ends.</t>
   </si>
   <si>
+    <t>"The more of an actor you become the less acting you want to do. Real ones pls read this again and again" ~ Deyemi Okanlawon</t>
+  </si>
+  <si>
+    <t>You wey be General Overseer, Men Are Scum chapel! 😂</t>
+  </si>
+  <si>
     <t>I wish you all a love that's deep, a love that's true, and most especially a love that starts with you... Happy Valentine's Day! 🌹🌹🌹</t>
   </si>
   <si>
+    <t>There's so much power in being underestimated.. use it! #thisisnotabout #3WorkingDays #butletspretenditis</t>
+  </si>
+  <si>
+    <t>Why you think say I dey go church gan? 🤷🏽‍♂️😊</t>
+  </si>
+  <si>
+    <t>Having a 6-pack when you're poor is not really the flex you think it is... this is the reply I'll be using for everyone who says "you dey suck bele" in 2024! 😂</t>
+  </si>
+  <si>
+    <t>I see what you did there Lord! You sha had to make it such that only You can take all the Glory... but na me come chop cane of humility. Thank You sha... I no dey complain! 🙏🏾 😂🙏🏾 #AllsFairInLove #imcinemas</t>
+  </si>
+  <si>
+    <t>We may have reached a critical moment in Nigeria... a time when the majority who failed due to their own lack of wisdom/character &amp; have lost hope of happiness turn with bitter, vengeful envy against those to worked hard to build successful lives &amp; to find their own happiness! 🥲</t>
+  </si>
+  <si>
+    <t>Nacking is not a sport sah</t>
+  </si>
+  <si>
+    <t>There's so much one can learn from mistakes and failure... but you first have to get past the fear and despair</t>
+  </si>
+  <si>
+    <t>My first attempt at producing a movie is #AllsFairInLove and I'm here on Twitter humbly asking for your insightful feedback and critiquing! Pores my heart and soul into this so do be gentle! #nowshowingon 😎😊</t>
+  </si>
+  <si>
+    <t>Watching an aged loved one slowly slip away is perhaps the most painful experience ever.... trying to be strong for others all day but now in the darkness of my room the tears flow freely. Lord pls grant me strength for tomorrow! 🙏🏾🙏🏾🙏🏾</t>
+  </si>
+  <si>
+    <t>Remember how they say looks can be deceiving? 🤦🏽‍♂️</t>
+  </si>
+  <si>
+    <t>the 3WD team and I decided to take time out from our intense marketing campaign to support with paying hospital bills for some of the children at Randle General Hospital, Surulere.</t>
+  </si>
+  <si>
     <t>I always try to add a lil extra whenever I take a cab... a bit more when the driver is a lady</t>
   </si>
   <si>
-    <t>Woke up to the sad news that a long time family friend's parents were assassinated in their home sometime last night/this morning. Their son stopped by on his way to the airport and found them slain... my brohter is still there trying console him. RIP Uncle &amp;amp; Aunty E!</t>
+    <t>Is it me or are most ppl not even trying to be anywhere near excellent but rather choose to be demonically stubborn in mediocrity! 🤦🏽‍♂️</t>
+  </si>
+  <si>
+    <t>You can almost cut through the hate in the atmosphere... 🤦🏽‍♂️</t>
+  </si>
+  <si>
+    <t>Becos beans be protein no mean say make you disrespect meat...</t>
+  </si>
+  <si>
+    <t>Usually many reasons one is not yet as successful as they want in one's career... none of those reasons include ppl who are legitimately succeeding in the same field. Pls use your hunger for success as fuel for your craft &amp; strategy not for blaming those ahead on the queue 🙏🏾</t>
+  </si>
+  <si>
+    <t>It's actually so much easier to forgive when you're truly successful and fulfilled</t>
+  </si>
+  <si>
+    <t>It's worrisome how my fellow upcoming actors assume success comes overnight. Yet if you check closely only a few have a vision, a strategy, an actionable plan, a USP or distinct brand identity.</t>
+  </si>
+  <si>
+    <t>The beauty of failure is that, if you are wise, with each one you increase your chances of success...</t>
+  </si>
+  <si>
+    <t>How do you present and promote yourself to producers, media and audiences? What else can you offer the industry while you wait? How else can you earn within and outside the industry?</t>
+  </si>
+  <si>
+    <t>The first thing that would happen is you won't dare start a conversation with "do you live under a rock" cos you'll have no human rights to fall back on if the person is higher on the communist hierarchy 🙂</t>
+  </si>
+  <si>
+    <t>WHY ARE YOU JAPA-ING? Are you attempting to JAPA from suffering you have no SOLUTION to and have had endure OR are you convinced about an OPPORTUNITY you are uniquely positioned to harness in another geographical region?</t>
+  </si>
+  <si>
+    <t>This woman's mouth is not good... which kind early morning yab be this! 🥲😂</t>
+  </si>
+  <si>
+    <t>My dear Aunty Betty pls we kindly request you publish your bank account... na woman wey dey take care of us and our deserving Egbons we wan dey credit this 2024! 😁😘 #wenodeygreeforanybodyelse</t>
+  </si>
+  <si>
+    <t>Hunger is an excuse for mediocrity? 👀</t>
+  </si>
+  <si>
+    <t>Not me! Make my woman come drag me for here ba? 😂</t>
+  </si>
+  <si>
+    <t>Social media dey taya me... must be an age thing 🤦🏽‍♂️</t>
+  </si>
+  <si>
+    <t>Earlier today... She: Forget what you see o, I didn't grow up in the trenches Me: No dear, the trenches grew up in you! (I'm still laughing)</t>
+  </si>
+  <si>
+    <t>My pastor say make I no dey fight pain wey get too much Holy Spirit! 👀😂</t>
+  </si>
+  <si>
+    <t>You must never let the size of your dream be limited by the condition of your environment!</t>
+  </si>
+  <si>
+    <t>I discovered something super cool about myself recently! Someone mentioned it in passing and it dawned on me that there's been traces of it my entire life but it was left unarticulated... I have a super power! 😄😄😄</t>
+  </si>
+  <si>
+    <t>Hmm... my dear sis I've been holding my tongue since. Anyway na awa rampant semi-literacy I blame! 🤦🏽‍♂️</t>
+  </si>
+  <si>
+    <t>Pesin: Hello, how are you? Me: I'm fine Pesin: *silence Me: *silence This 2024 no go dey ask "how are you" if you never ready to carry gbese</t>
+  </si>
+  <si>
+    <t>Just occurred to me that I focused too much on the handful of ppl who caused me pain than on the many who have brought me joy... and now the world seems ever so slightly brighter! 😊</t>
+  </si>
+  <si>
+    <t>You see the trap you set for yasef?</t>
+  </si>
+  <si>
+    <t>Sigh... I get bad mouth o! #ifnobesay #ideysellmarket #3WorkingDays #incinemasOctober18</t>
+  </si>
+  <si>
+    <t>All these WhatsApp texts of "Deyemi come back o"... if na you you go come back? 🙄👀🚶🏽‍♂️</t>
+  </si>
+  <si>
+    <t>Lol... that's like me saying I hope you're not as stupid as this comment in real life. It's not funny, it's insulting 🙂</t>
+  </si>
+  <si>
+    <t>What are you known for being excellent at?</t>
+  </si>
+  <si>
+    <t>I suspect that no intelligent Nollywood filmmaker has issues with constructive criticism... perhaps it's ppl with Dunning-Kruger syndrome, unintelligent comments/insults and paid saboteur critiques they may have issues with! 😂😂😂 cc</t>
+  </si>
+  <si>
+    <t>It's actually crazy how most Nigerians keep making the same mistake cos they NEVER research their history. EVERYTHING happening now has happened before and yet the woke generation of that time is being castigated by the woke generation of this day... let's kuku wait and see</t>
+  </si>
+  <si>
+    <t>If na charity I no go mind o... na red I dey see lie this! 😂😂😂</t>
+  </si>
+  <si>
+    <t>Nope. When I'm in rest mode I tend to humour idiots 🙂</t>
+  </si>
+  <si>
+    <t>Na why she no gree pick my calls.... my voice sabi convince pesin! 😂😂😂</t>
+  </si>
+  <si>
+    <t>Under Emperor Constantine, the Church in Rome began celebrating Christmas on Dec. 25 in 336 AD. Some say the date was chosen to outshine the Sol Invictus and pagan celebrations.</t>
   </si>
 </sst>
 </file>
@@ -437,7 +788,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A22"/>
+  <dimension ref="A1:A139"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -550,6 +901,591 @@
         <v>21</v>
       </c>
     </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139" t="s">
+        <v>138</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
